--- a/Resultados/Entregable/Reporte.xlsx
+++ b/Resultados/Entregable/Reporte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\Ivan\Laboral\EstrategiaSur\GitProjects\Proyeccion-electoral-congreso\Resultados\Entregable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9642146F-3C0F-4FFC-BB67-BEA1C3988F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2408E2A8-D5D0-413C-9D88-8048D4BB643B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1665" windowWidth="29040" windowHeight="15720" activeTab="13" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
+    <workbookView xWindow="-28920" yWindow="1665" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
   </bookViews>
   <sheets>
     <sheet name="D3" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="46">
   <si>
     <t>Esc</t>
   </si>
@@ -309,32 +309,6 @@
       </rPr>
       <t xml:space="preserve">
 -  Los resultados presentados son el producto de un modelo mixto que combina variables determinísticas y probabilísticas. Las variables determinísticas están basadas en datos observables y predecibles, mientras que las probabilísticas buscan capturar aquellas dinámicas que no se pueden predecir completamente a partir de mediciones conocidas. Esto permite modelar incertidumbres inherentes al sistema. Aunque los resultados no representan la realidad al 100%, se estima que los resultados reales estarán dentro de un rango cercano, considerando un margen de error razonable.
-- Se asumió el supuesto de que Catalina Pérez buscará la reelección por el partido FREVS. Dado que el modelo considera un aumento en la votación de los partidos en territorios donde compite un candidato incumbente, este escenario probablemente influyó en un incremento de la votación del FREVS en desmedro del Frente Amplio.
-- El caso de Yovana Ahumadaes otro caso relevante para analizar. En el modelo, se consideró a Ahumada como incumbente del Partido Socialcristiano (PSC) en lugar de como parte del Partido de la Gente (PDG). Se destaca que en el escenario "Partidos", el PDG le quitó el cupo, donde el modelo sugiere que el PDG mantiene una fortaleza en el distrito más allá de los personalismos. Sin embargo, la falta de alianzas del PDG en los demás escenarios lo relega de la posibilidad de integrar un escaño.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Algunos puntos a tener en cuenta sobre los resultados del modelo:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
--  Los resultados presentados son el producto de un modelo mixto que combina variables determinísticas y probabilísticas. Las variables determinísticas están basadas en datos observables y predecibles, mientras que las probabilísticas buscan capturar aquellas dinámicas que no se pueden predecir completamente a partir de mediciones conocidas. Esto permite modelar incertidumbres inherentes al sistema. Aunque los resultados no representan la realidad al 100%, se estima que los resultados reales estarán dentro de un rango cercano, considerando un margen de error razonable.
 - Marcela Riquelme va como incumbente del FREVS, Marta Gonzalez como incumbente del PPD y Natalia Romero como incumbente de la UDI.</t>
     </r>
   </si>
@@ -445,6 +419,41 @@
     </r>
   </si>
   <si>
+    <t>Simulacion</t>
+  </si>
+  <si>
+    <t>Simulación</t>
+  </si>
+  <si>
+    <t>Mismos pactos de la convención. Para aquellos partidos no constituidos en su época se tomaron supuestos de acuerdo a los candidatos que se llevaron en cada pacto. Por ejemplo, Republicanos va dentro de CHV y Amarillos y Democratas dentro de SD</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Algunos puntos a tener en cuenta sobre los resultados del modelo:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+-  Los resultados presentados son el producto de un modelo mixto que combina variables determinísticas y probabilísticas. Las variables determinísticas están basadas en datos observables y predecibles, mientras que las probabilísticas buscan capturar aquellas dinámicas que no se pueden predecir completamente a partir de mediciones conocidas. Esto permite modelar incertidumbres inherentes al sistema. Aunque los resultados no representan la realidad al 100%, se estima que los resultados reales estarán dentro de un rango cercano, considerando un margen de error razonable.
+- Se asumió el supuesto de que Catalina Pérez buscará la reelección por el partido FREVS. Dado que el modelo considera un aumento en la votación de los partidos en territorios donde compite un candidato incumbente, este escenario probablemente influyó en un incremento de la votación del FREVS en desmedro del Frente Amplio.
+- El caso de Yovana Ahumadaes otro caso relevante para analizar. En el modelo, se consideró a Ahumada como incumbente del Partido Socialcristiano (PSC) en lugar de como parte del Partido de la Gente (PDG). Se destaca que en algunos escenarios, el PDG le quitó el cupo, donde el modelo sugiere que el PDG mantiene una fortaleza en el distrito más allá de los personalismos. Sin embargo, la falta de alianzas del PDG en los demás escenarios lo relega de la posibilidad de integrar un escaño.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -467,17 +476,9 @@
       <t xml:space="preserve">
 -  Los resultados presentados son el producto de un modelo mixto que combina variables determinísticas y probabilísticas. Las variables determinísticas están basadas en datos observables y predecibles, mientras que las probabilísticas buscan capturar aquellas dinámicas que no se pueden predecir completamente a partir de mediciones conocidas. Esto permite modelar incertidumbres inherentes al sistema. Aunque los resultados no representan la realidad al 100%, se estima que los resultados reales estarán dentro de un rango cercano, considerando un margen de error razonable.
 - Carlos Bianchi se considera como Independiente y Christian Matheson como Evopoli
+- Hay que estar atentos a la definición que tome Bianchi. El modelo no fue capaz de predecir la votación de su figura
 </t>
     </r>
-  </si>
-  <si>
-    <t>Simulacion</t>
-  </si>
-  <si>
-    <t>Simulación</t>
-  </si>
-  <si>
-    <t>Mismos pactos de la convención. Para aquellos partidos no constituidos en su época se tomaron supuestos de acuerdo a los candidatos que se llevaron en cada pacto. Por ejemplo, Republicanos va dentro de CHV y Amarillos y Democratas dentro de SD</t>
   </si>
 </sst>
 </file>
@@ -536,7 +537,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -680,22 +681,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -706,6 +789,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -720,12 +806,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,16 +862,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>88899</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>3219450</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>76609</xdr:rowOff>
+      <xdr:rowOff>73434</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -864,13 +972,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>88899</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>3286215</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -1029,16 +1137,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>88899</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>3343354</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>3340179</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>146049</xdr:rowOff>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1084,16 +1192,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>88899</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>3326424</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>130175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1201,7 +1309,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>3150779</xdr:colOff>
+      <xdr:colOff>3153954</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
@@ -1256,9 +1364,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>3207917</xdr:colOff>
+      <xdr:colOff>3211092</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>69849</xdr:rowOff>
+      <xdr:rowOff>66674</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1470,14 +1578,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>85724</xdr:colOff>
+      <xdr:colOff>88898</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>2525092</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85045</xdr:colOff>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1507,8 +1615,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8670924" y="38100"/>
-          <a:ext cx="3569668" cy="2009775"/>
+          <a:off x="7146923" y="38100"/>
+          <a:ext cx="4212547" cy="2371725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1533,7 +1641,7 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>3371850</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>159237</xdr:rowOff>
+      <xdr:rowOff>162412</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1892,444 +2000,472 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89480051-BCA3-405F-B673-471E1D4EE818}">
-  <dimension ref="B2:P19"/>
+  <dimension ref="B2:Q19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.26953125" customWidth="1"/>
-    <col min="16" max="16" width="46.54296875" customWidth="1"/>
+    <col min="16" max="16" width="16.26953125" customWidth="1"/>
+    <col min="17" max="17" width="46.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="N2" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16">
-        <v>0</v>
-      </c>
-      <c r="E3" s="16">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16">
-        <v>1</v>
-      </c>
-      <c r="H3" s="16">
-        <v>1</v>
-      </c>
-      <c r="I3" s="16">
-        <v>0</v>
-      </c>
-      <c r="J3" s="16">
-        <v>0</v>
-      </c>
-      <c r="K3" s="16">
-        <v>0</v>
-      </c>
-      <c r="L3" s="16">
-        <v>0</v>
-      </c>
-      <c r="M3" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="19">
-        <v>3.9578039820328599E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>6.4451978823325803E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>4.03730828633087E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>1.90826063356959E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>6.3613407698177304E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>2.2958703387586099E-2</v>
-      </c>
-      <c r="I4" s="19">
-        <v>5.1489001292731498E-2</v>
-      </c>
-      <c r="J4" s="19">
-        <v>5.5926243500287097E-2</v>
-      </c>
-      <c r="K4" s="19">
-        <v>9.82816896237967E-2</v>
-      </c>
-      <c r="L4" s="19">
-        <v>4.2748772167200202E-2</v>
-      </c>
-      <c r="M4" s="19">
-        <v>4.5141767817014199E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <v>0</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="9">
+        <v>3.9728629351804802E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>6.4351469435161596E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>4.0330324160457502E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>1.9177711714809201E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>6.4052194404028595E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>2.3110741195758299E-2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>5.1421320541902599E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>5.4517847483993201E-2</v>
+      </c>
+      <c r="K4" s="9">
+        <v>9.8424272410510993E-2</v>
+      </c>
+      <c r="L4" s="9">
+        <v>4.3276427400384898E-2</v>
+      </c>
+      <c r="M4" s="9">
+        <v>4.4834649234987999E-2</v>
+      </c>
+      <c r="N4" s="9">
+        <v>4.0616496081645997E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17">
-        <v>1</v>
-      </c>
-      <c r="E5" s="17">
-        <v>0</v>
-      </c>
-      <c r="F5" s="17">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17">
-        <v>1</v>
-      </c>
-      <c r="H5" s="17">
-        <v>0</v>
-      </c>
-      <c r="I5" s="17">
-        <v>1</v>
-      </c>
-      <c r="J5" s="17">
-        <v>1</v>
-      </c>
-      <c r="K5" s="17">
-        <v>1</v>
-      </c>
-      <c r="L5" s="17">
-        <v>0</v>
-      </c>
-      <c r="M5" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1</v>
+      </c>
+      <c r="K5" s="7">
+        <v>1</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
+        <v>1</v>
+      </c>
+      <c r="L7" s="7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="8"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="10"/>
-      <c r="O15" s="4" t="s">
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>1</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="2:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="23"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B12" s="24"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="25"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B13" s="24"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="25"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B14" s="24"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="25"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B15" s="24"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="25"/>
+      <c r="P15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="Q15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="10"/>
-      <c r="O16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P16" s="2" t="s">
+    <row r="16" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="24"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="25"/>
+      <c r="P16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="10"/>
-      <c r="O17" s="1" t="s">
+    <row r="17" spans="2:17" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="24"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="25"/>
+      <c r="P17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="10"/>
-      <c r="O18" s="1" t="s">
+      <c r="Q17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="24"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="25"/>
+      <c r="P18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="Q18" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="13"/>
-      <c r="O19" s="1" t="s">
+    <row r="19" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="28"/>
+      <c r="P19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B11:M19"/>
+    <mergeCell ref="B11:N19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2347,25 +2483,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2373,68 +2509,68 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16">
-        <v>1</v>
-      </c>
-      <c r="H3" s="16">
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>5.4990858856109902E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>7.1981815423462506E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>8.8073314288212107E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>0.116888874032208</v>
-      </c>
-      <c r="G4" s="19">
-        <v>0.14097469535948701</v>
-      </c>
-      <c r="H4" s="19">
-        <v>9.6606077125026696E-2</v>
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>5.4130507718941102E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>7.0242946633112494E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>8.6427243786159999E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.115904809087334</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.138012856552231</v>
+      </c>
+      <c r="H4" s="9">
+        <v>9.5287061013211202E-2</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17">
-        <v>1</v>
-      </c>
-      <c r="F5" s="17">
-        <v>1</v>
-      </c>
-      <c r="G5" s="17">
-        <v>1</v>
-      </c>
-      <c r="H5" s="17">
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
         <v>1</v>
       </c>
     </row>
@@ -2446,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -2458,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.35">
@@ -2492,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2504,71 +2640,71 @@
         <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
+      <c r="B11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="10"/>
-      <c r="J15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15"/>
+      <c r="J15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="10"/>
+    <row r="16" spans="2:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="15"/>
       <c r="J16" s="1" t="s">
         <v>2</v>
       </c>
@@ -2577,28 +2713,28 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="87" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="15"/>
       <c r="J17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15"/>
       <c r="J18" s="1" t="s">
         <v>4</v>
       </c>
@@ -2607,13 +2743,13 @@
       </c>
     </row>
     <row r="19" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
       <c r="J19" s="1" t="s">
         <v>5</v>
       </c>
@@ -2632,383 +2768,413 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07F82A79-2B4A-4137-852C-755DEDCA5B93}">
-  <dimension ref="B2:N19"/>
+  <dimension ref="B2:O19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.26953125" customWidth="1"/>
-    <col min="14" max="14" width="47.90625" customWidth="1"/>
+    <col min="14" max="14" width="16.26953125" customWidth="1"/>
+    <col min="15" max="15" width="47.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="14" t="s">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="15">
-        <v>1</v>
-      </c>
-      <c r="D3" s="15">
-        <v>1</v>
-      </c>
-      <c r="E3" s="15">
-        <v>1</v>
-      </c>
-      <c r="F3" s="15">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15">
-        <v>1</v>
-      </c>
-      <c r="H3" s="15">
-        <v>1</v>
-      </c>
-      <c r="I3" s="15">
-        <v>0</v>
-      </c>
-      <c r="J3" s="15">
-        <v>0</v>
-      </c>
-      <c r="K3" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>3.6286167150202102E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>6.4811029090542496E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>3.9159026245337299E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>7.4816153820304002E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>0.10370821805025</v>
-      </c>
-      <c r="H4" s="19">
-        <v>0.120443051090475</v>
-      </c>
-      <c r="I4" s="19">
-        <v>7.3914075364331797E-2</v>
-      </c>
-      <c r="J4" s="19">
-        <v>0.107392492690959</v>
-      </c>
-      <c r="K4" s="19">
-        <v>5.2960791616726198E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="15">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15">
-        <v>0</v>
-      </c>
-      <c r="E5" s="15">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15">
-        <v>1</v>
-      </c>
-      <c r="G5" s="15">
-        <v>1</v>
-      </c>
-      <c r="H5" s="15">
-        <v>1</v>
-      </c>
-      <c r="I5" s="15">
-        <v>1</v>
-      </c>
-      <c r="J5" s="15">
-        <v>1</v>
-      </c>
-      <c r="K5" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B6" s="15" t="s">
+      <c r="L2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>3.6372893789000403E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>6.5278363769419298E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>3.9555221002312603E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>7.3932311596562203E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.102279068355299</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.119771224210115</v>
+      </c>
+      <c r="I4" s="9">
+        <v>7.3328929235358498E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0.10602359856681801</v>
+      </c>
+      <c r="K4" s="9">
+        <v>5.2697021440837898E-2</v>
+      </c>
+      <c r="L4" s="9">
+        <v>4.2105898664567203E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="15">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15">
-        <v>1</v>
-      </c>
-      <c r="G6" s="15">
-        <v>1</v>
-      </c>
-      <c r="H6" s="15">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15">
-        <v>1</v>
-      </c>
-      <c r="J6" s="15">
-        <v>1</v>
-      </c>
-      <c r="K6" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B7" s="15" t="s">
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="15">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15">
-        <v>1</v>
-      </c>
-      <c r="G7" s="15">
-        <v>1</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15">
-        <v>0</v>
-      </c>
-      <c r="J7" s="15">
-        <v>1</v>
-      </c>
-      <c r="K7" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B8" s="15" t="s">
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="15">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15">
-        <v>1</v>
-      </c>
-      <c r="G8" s="15">
-        <v>1</v>
-      </c>
-      <c r="H8" s="15">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15">
-        <v>0</v>
-      </c>
-      <c r="J8" s="15">
-        <v>1</v>
-      </c>
-      <c r="K8" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="2:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="10"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="10"/>
-      <c r="M15" s="4" t="s">
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="23"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B12" s="24"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="24"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="25"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="24"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="24"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="25"/>
+      <c r="N15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="O15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="10"/>
-      <c r="M16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N16" s="2" t="s">
+    <row r="16" spans="2:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="24"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="25"/>
+      <c r="N16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="10"/>
-      <c r="M17" s="1" t="s">
+    <row r="17" spans="2:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="24"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="25"/>
+      <c r="N17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="10"/>
-      <c r="M18" s="1" t="s">
+      <c r="O17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="24"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="25"/>
+      <c r="N18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="13"/>
-      <c r="M19" s="1" t="s">
+    <row r="19" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="28"/>
+      <c r="N19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B11:K19"/>
+    <mergeCell ref="B11:L19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3027,282 +3193,282 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="14" t="s">
+      <c r="D2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="15">
-        <v>1</v>
-      </c>
-      <c r="D3" s="15">
-        <v>1</v>
-      </c>
-      <c r="E3" s="15">
-        <v>0</v>
-      </c>
-      <c r="F3" s="15">
-        <v>1</v>
-      </c>
-      <c r="G3" s="15">
-        <v>2</v>
-      </c>
-      <c r="H3" s="15">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15">
-        <v>2</v>
-      </c>
-      <c r="J3" s="15">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>5.98266966803968E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>3.0713882511829601E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>4.85215761219231E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>9.4973927571876296E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>0.119274988912519</v>
-      </c>
-      <c r="H4" s="19">
-        <v>5.1207886067056098E-2</v>
-      </c>
-      <c r="I4" s="19">
-        <v>0.135176852299637</v>
-      </c>
-      <c r="J4" s="19">
-        <v>3.9563154913389402E-2</v>
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>5.8483210793431703E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>3.0378429112220998E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>4.1397196446809802E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>9.4143626620646098E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.116212404213865</v>
+      </c>
+      <c r="H4" s="9">
+        <v>5.0766852739215301E-2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.13153013347814499</v>
+      </c>
+      <c r="J4" s="9">
+        <v>3.92420788719565E-2</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="15">
-        <v>1</v>
-      </c>
-      <c r="D5" s="15">
-        <v>0</v>
-      </c>
-      <c r="E5" s="15">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15">
-        <v>1</v>
-      </c>
-      <c r="G5" s="15">
-        <v>2</v>
-      </c>
-      <c r="H5" s="15">
-        <v>1</v>
-      </c>
-      <c r="I5" s="15">
-        <v>2</v>
-      </c>
-      <c r="J5" s="15">
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="15">
-        <v>1</v>
-      </c>
-      <c r="D6" s="15">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15">
-        <v>1</v>
-      </c>
-      <c r="F6" s="15">
-        <v>1</v>
-      </c>
-      <c r="G6" s="15">
-        <v>1</v>
-      </c>
-      <c r="H6" s="15">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15">
-        <v>2</v>
-      </c>
-      <c r="J6" s="15">
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>2</v>
+      </c>
+      <c r="J6" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="15">
-        <v>1</v>
-      </c>
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15">
-        <v>1</v>
-      </c>
-      <c r="G7" s="15">
-        <v>1</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15">
-        <v>2</v>
-      </c>
-      <c r="J7" s="15">
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="15">
-        <v>1</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15">
-        <v>1</v>
-      </c>
-      <c r="G8" s="15">
-        <v>1</v>
-      </c>
-      <c r="H8" s="15">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15">
-        <v>2</v>
-      </c>
-      <c r="J8" s="15">
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2</v>
+      </c>
+      <c r="J8" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="B11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="10"/>
-      <c r="L15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
+      <c r="L15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="10"/>
+    <row r="16" spans="2:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
       <c r="L16" s="1" t="s">
         <v>2</v>
       </c>
@@ -3311,32 +3477,32 @@
       </c>
     </row>
     <row r="17" spans="2:13" ht="69.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
       <c r="L17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
       <c r="L18" s="1" t="s">
         <v>4</v>
       </c>
@@ -3345,15 +3511,15 @@
       </c>
     </row>
     <row r="19" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="18"/>
       <c r="L19" s="1" t="s">
         <v>5</v>
       </c>
@@ -3382,253 +3548,255 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="15">
-        <v>1</v>
-      </c>
-      <c r="D3" s="15">
-        <v>1</v>
-      </c>
-      <c r="E3" s="15">
-        <v>1</v>
-      </c>
-      <c r="F3" s="15">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15">
-        <v>0</v>
-      </c>
-      <c r="H3" s="15">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>7.3970719249892E-2</v>
-      </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19">
-        <v>6.8646709410358206E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>0.111774475214431</v>
-      </c>
-      <c r="G4" s="19">
-        <v>7.4224740293475103E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>0.123706161809839</v>
-      </c>
-      <c r="I4" s="19">
-        <v>0.184295135940378</v>
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>7.1749687926160793E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2.86728400357071E-3</v>
+      </c>
+      <c r="E4" s="9">
+        <v>6.9961209780687802E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.11061425385887499</v>
+      </c>
+      <c r="G4" s="9">
+        <v>7.4292030406208007E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.12438605548545401</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.18340167503456001</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="15">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15">
-        <v>0</v>
-      </c>
-      <c r="E5" s="15">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15">
-        <v>1</v>
-      </c>
-      <c r="G5" s="15">
-        <v>1</v>
-      </c>
-      <c r="H5" s="15">
-        <v>1</v>
-      </c>
-      <c r="I5" s="15">
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="15">
-        <v>1</v>
-      </c>
-      <c r="D6" s="15">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15">
-        <v>1</v>
-      </c>
-      <c r="G6" s="15">
-        <v>0</v>
-      </c>
-      <c r="H6" s="15">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15">
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="15">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15">
-        <v>1</v>
-      </c>
-      <c r="G7" s="15">
-        <v>1</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15">
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="15">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15">
-        <v>1</v>
-      </c>
-      <c r="G8" s="15">
-        <v>1</v>
-      </c>
-      <c r="H8" s="15">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15">
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
+      <c r="B11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="10"/>
-      <c r="K15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
+      <c r="K15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="10"/>
+    <row r="16" spans="2:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
       <c r="K16" s="1" t="s">
         <v>2</v>
       </c>
@@ -3637,30 +3805,30 @@
       </c>
     </row>
     <row r="17" spans="2:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
       <c r="K17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
       <c r="K18" s="1" t="s">
         <v>4</v>
       </c>
@@ -3669,14 +3837,14 @@
       </c>
     </row>
     <row r="19" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="18"/>
       <c r="K19" s="1" t="s">
         <v>5</v>
       </c>
@@ -3695,322 +3863,292 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD025208-EBF5-4B5B-AA05-51C599203D1C}">
-  <dimension ref="B2:L19"/>
+  <dimension ref="B2:K19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.26953125" customWidth="1"/>
-    <col min="12" max="12" width="48.453125" customWidth="1"/>
+    <col min="10" max="10" width="16.26953125" customWidth="1"/>
+    <col min="11" max="11" width="48.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="14" t="s">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="14" t="s">
+      <c r="G2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="H2" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="15">
-        <v>1</v>
-      </c>
-      <c r="D3" s="15">
-        <v>1</v>
-      </c>
-      <c r="E3" s="15">
-        <v>2</v>
-      </c>
-      <c r="F3" s="15">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15">
-        <v>0</v>
-      </c>
-      <c r="H3" s="15">
-        <v>1</v>
-      </c>
-      <c r="I3" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>5.8962562028244597E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>2.60497854562254E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>0.19765904656812999</v>
-      </c>
-      <c r="F4" s="19">
-        <v>9.9678516706495399E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>5.05906185707495E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>0.1190169541099</v>
-      </c>
-      <c r="I4" s="19">
-        <v>7.3278498093867397E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="15">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15">
-        <v>0</v>
-      </c>
-      <c r="E5" s="15">
-        <v>2</v>
-      </c>
-      <c r="F5" s="15">
-        <v>1</v>
-      </c>
-      <c r="G5" s="15">
-        <v>0</v>
-      </c>
-      <c r="H5" s="15">
-        <v>1</v>
-      </c>
-      <c r="I5" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="15" t="s">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>5.8698241104487597E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2.5696974911509199E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.197973677581186</v>
+      </c>
+      <c r="F4" s="9">
+        <v>9.9390564483803998E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.11689058413233901</v>
+      </c>
+      <c r="H4" s="9">
+        <v>7.3045394734937097E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="15">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15">
-        <v>1</v>
-      </c>
-      <c r="F6" s="15">
-        <v>1</v>
-      </c>
-      <c r="G6" s="15">
-        <v>1</v>
-      </c>
-      <c r="H6" s="15">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="15" t="s">
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>2</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="15">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15">
-        <v>2</v>
-      </c>
-      <c r="F7" s="15">
-        <v>1</v>
-      </c>
-      <c r="G7" s="15">
-        <v>0</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="15" t="s">
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="15">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
-        <v>2</v>
-      </c>
-      <c r="F8" s="15">
-        <v>1</v>
-      </c>
-      <c r="G8" s="15">
-        <v>0</v>
-      </c>
-      <c r="H8" s="15">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="10"/>
-      <c r="K15" s="4" t="s">
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15"/>
+      <c r="J15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="10"/>
-      <c r="K16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L16" s="2" t="s">
+    <row r="16" spans="2:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="15"/>
+      <c r="J16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="10"/>
-      <c r="K17" s="1" t="s">
+    <row r="17" spans="2:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="15"/>
+      <c r="J17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="10"/>
-      <c r="K18" s="1" t="s">
+      <c r="K17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15"/>
+      <c r="J18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="13"/>
-      <c r="K19" s="1" t="s">
+    <row r="19" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
+      <c r="J19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B11:I19"/>
+    <mergeCell ref="B11:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4019,320 +4157,352 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9D3998-67DE-4085-A6E8-30E813E46135}">
-  <dimension ref="B2:L19"/>
+  <dimension ref="B2:M19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.26953125" customWidth="1"/>
-    <col min="12" max="12" width="48.54296875" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" customWidth="1"/>
+    <col min="13" max="13" width="48.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="14" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="15">
-        <v>1</v>
-      </c>
-      <c r="D3" s="15">
-        <v>1</v>
-      </c>
-      <c r="E3" s="15">
-        <v>1</v>
-      </c>
-      <c r="F3" s="15">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15">
-        <v>0</v>
-      </c>
-      <c r="H3" s="15">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>7.9650774710701797E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>3.6093603246519203E-2</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19">
-        <v>0.100470201844183</v>
-      </c>
-      <c r="G4" s="19">
-        <v>8.3810820549474502E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>8.6080607718162394E-2</v>
-      </c>
-      <c r="I4" s="19">
-        <v>9.7927213227085003E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="15">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15">
-        <v>0</v>
-      </c>
-      <c r="E5" s="15">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15">
-        <v>1</v>
-      </c>
-      <c r="G5" s="15">
-        <v>0</v>
-      </c>
-      <c r="H5" s="15">
-        <v>1</v>
-      </c>
-      <c r="I5" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="15" t="s">
+      <c r="J2" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>7.9515312095265994E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>3.5634370934137002E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>7.5723223467975397E-3</v>
+      </c>
+      <c r="F4" s="9">
+        <v>9.9662727873555498E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>8.4884103457780205E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>8.6865354921120394E-2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>9.7531808199446901E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>6.5271640393227207E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="15">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15">
-        <v>1</v>
-      </c>
-      <c r="G6" s="15">
-        <v>0</v>
-      </c>
-      <c r="H6" s="15">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="15" t="s">
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="15">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15">
-        <v>1</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="15" t="s">
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="15">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15">
-        <v>1</v>
-      </c>
-      <c r="H8" s="15">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="10"/>
-      <c r="K15" s="4" t="s">
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B12" s="24"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="25"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B13" s="24"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="25"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B14" s="24"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="25"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B15" s="24"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="25"/>
+      <c r="L15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="10"/>
-      <c r="K16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L16" s="2" t="s">
+    <row r="16" spans="2:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="24"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="25"/>
+      <c r="L16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="10"/>
-      <c r="K17" s="1" t="s">
+    <row r="17" spans="2:13" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="24"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="25"/>
+      <c r="L17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="10"/>
-      <c r="K18" s="1" t="s">
+      <c r="M17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="24"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="25"/>
+      <c r="L18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="13"/>
-      <c r="K19" s="1" t="s">
+    <row r="19" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
+      <c r="L19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B11:I19"/>
+    <mergeCell ref="B11:J19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4351,31 +4521,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4383,86 +4553,86 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16">
-        <v>2</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16">
-        <v>0</v>
-      </c>
-      <c r="H3" s="16">
-        <v>1</v>
-      </c>
-      <c r="I3" s="16">
-        <v>0</v>
-      </c>
-      <c r="J3" s="16">
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="19">
-        <v>4.9027020929010401E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>5.8436578929330303E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>0.12537663936299001</v>
-      </c>
-      <c r="F4" s="19">
-        <v>2.94699773802179E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>8.3193744716338794E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>7.4340756163319394E-2</v>
-      </c>
-      <c r="I4" s="19">
-        <v>8.21670008225375E-2</v>
-      </c>
-      <c r="J4" s="19">
-        <v>5.9370501747892199E-2</v>
+      <c r="B4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="9">
+        <v>4.8825020869699802E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>5.8101032329737297E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.124751128165944</v>
+      </c>
+      <c r="F4" s="9">
+        <v>2.9232429940214098E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>8.3171190232308595E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>7.3513318952303897E-2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>8.1328009453151995E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>5.92289330942702E-2</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17">
-        <v>1</v>
-      </c>
-      <c r="E5" s="17">
-        <v>2</v>
-      </c>
-      <c r="F5" s="17">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17">
-        <v>1</v>
-      </c>
-      <c r="H5" s="17">
-        <v>1</v>
-      </c>
-      <c r="I5" s="17">
-        <v>1</v>
-      </c>
-      <c r="J5" s="17">
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4553,82 +4723,80 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H10" s="5"/>
-    </row>
+    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="10"/>
-      <c r="L15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
+      <c r="L15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="10"/>
+    <row r="16" spans="2:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
       <c r="L16" s="1" t="s">
         <v>2</v>
       </c>
@@ -4637,32 +4805,32 @@
       </c>
     </row>
     <row r="17" spans="2:13" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
       <c r="L17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
       <c r="L18" s="1" t="s">
         <v>4</v>
       </c>
@@ -4671,15 +4839,15 @@
       </c>
     </row>
     <row r="19" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="18"/>
       <c r="L19" s="1" t="s">
         <v>5</v>
       </c>
@@ -4707,34 +4875,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4742,93 +4910,95 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
-        <v>2</v>
-      </c>
-      <c r="D3" s="16">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16">
-        <v>2</v>
-      </c>
-      <c r="H3" s="16">
-        <v>0</v>
-      </c>
-      <c r="I3" s="16">
-        <v>0</v>
-      </c>
-      <c r="J3" s="16">
-        <v>1</v>
-      </c>
-      <c r="K3" s="16">
+      <c r="C3" s="6">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>2</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+      <c r="K3" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="19">
-        <v>7.0042566563821199E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>3.8425608501885498E-2</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19">
-        <v>5.23311621528968E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>0.129126956919209</v>
-      </c>
-      <c r="H4" s="19">
-        <v>5.7867672266026703E-2</v>
-      </c>
-      <c r="I4" s="19">
-        <v>5.98005942178036E-2</v>
-      </c>
-      <c r="J4" s="19">
-        <v>0.136383556165009</v>
-      </c>
-      <c r="K4" s="19">
-        <v>4.7135184550337099E-2</v>
+      <c r="B4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="9">
+        <v>6.9425565248754498E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>3.7866030973151998E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>1.3683190189580899E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>5.2078965758210999E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.12677577151101099</v>
+      </c>
+      <c r="H4" s="9">
+        <v>5.7300613151191303E-2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>5.8934086246928599E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0.13461120128040299</v>
+      </c>
+      <c r="K4" s="9">
+        <v>4.5954216541556701E-2</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
-        <v>1</v>
-      </c>
-      <c r="D5" s="17">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17">
-        <v>0</v>
-      </c>
-      <c r="F5" s="17">
-        <v>1</v>
-      </c>
-      <c r="G5" s="17">
-        <v>2</v>
-      </c>
-      <c r="H5" s="17">
-        <v>1</v>
-      </c>
-      <c r="I5" s="17">
-        <v>1</v>
-      </c>
-      <c r="J5" s="17">
-        <v>2</v>
-      </c>
-      <c r="K5" s="17">
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
+        <v>2</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
+        <v>2</v>
+      </c>
+      <c r="K5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -4852,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -4861,7 +5031,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
@@ -4928,88 +5098,86 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="5"/>
-    </row>
+    <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="15"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="15"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="15"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="10"/>
-      <c r="M15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="15"/>
+      <c r="M15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="10"/>
+    <row r="16" spans="2:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="15"/>
       <c r="M16" s="1" t="s">
         <v>2</v>
       </c>
@@ -5018,34 +5186,34 @@
       </c>
     </row>
     <row r="17" spans="2:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="15"/>
       <c r="M17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="15"/>
       <c r="M18" s="1" t="s">
         <v>4</v>
       </c>
@@ -5054,16 +5222,16 @@
       </c>
     </row>
     <row r="19" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="18"/>
       <c r="M19" s="1" t="s">
         <v>5</v>
       </c>
@@ -5091,34 +5259,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5126,95 +5294,95 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
-        <v>2</v>
-      </c>
-      <c r="D3" s="16">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16">
-        <v>1</v>
-      </c>
-      <c r="H3" s="16">
-        <v>0</v>
-      </c>
-      <c r="I3" s="16">
-        <v>1</v>
-      </c>
-      <c r="J3" s="16">
-        <v>1</v>
-      </c>
-      <c r="K3" s="16">
+      <c r="C3" s="6">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>1</v>
+      </c>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+      <c r="K3" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>0.116377267956215</v>
-      </c>
-      <c r="D4" s="19">
-        <v>3.1527365422102202E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>1.7503973609236698E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>3.3928325086219797E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>8.0185635027740301E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>6.7077222971959796E-2</v>
-      </c>
-      <c r="I4" s="19">
-        <v>6.2993552256710106E-2</v>
-      </c>
-      <c r="J4" s="19">
-        <v>0.148975858449542</v>
-      </c>
-      <c r="K4" s="19">
-        <v>4.3005248163142898E-2</v>
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.117177623026207</v>
+      </c>
+      <c r="D4" s="9">
+        <v>3.1792884302106902E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>1.7448295881612001E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>3.3219564503409703E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>8.0234742091864195E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>6.6257627389398693E-2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>6.2457418647637097E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0.15088268200380101</v>
+      </c>
+      <c r="K4" s="9">
+        <v>4.33985566896012E-2</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
-        <v>2</v>
-      </c>
-      <c r="D5" s="17">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17">
-        <v>0</v>
-      </c>
-      <c r="F5" s="17">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17">
-        <v>1</v>
-      </c>
-      <c r="H5" s="17">
-        <v>1</v>
-      </c>
-      <c r="I5" s="17">
-        <v>1</v>
-      </c>
-      <c r="J5" s="17">
+      <c r="C5" s="7">
+        <v>2</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
         <v>3</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5223,7 +5391,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -5232,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -5244,10 +5412,10 @@
         <v>1</v>
       </c>
       <c r="J6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
@@ -5314,88 +5482,86 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="5"/>
-    </row>
+    <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="15"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="15"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="15"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="10"/>
-      <c r="M15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="15"/>
+      <c r="M15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="10"/>
+    <row r="16" spans="2:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="15"/>
       <c r="M16" s="1" t="s">
         <v>2</v>
       </c>
@@ -5404,34 +5570,34 @@
       </c>
     </row>
     <row r="17" spans="2:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="15"/>
       <c r="M17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="15"/>
       <c r="M18" s="1" t="s">
         <v>4</v>
       </c>
@@ -5440,16 +5606,16 @@
       </c>
     </row>
     <row r="19" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="18"/>
       <c r="M19" s="1" t="s">
         <v>5</v>
       </c>
@@ -5477,31 +5643,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5509,86 +5675,86 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16">
-        <v>2</v>
-      </c>
-      <c r="H3" s="16">
-        <v>1</v>
-      </c>
-      <c r="I3" s="16">
-        <v>1</v>
-      </c>
-      <c r="J3" s="16">
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>2</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>1</v>
+      </c>
+      <c r="J3" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="19">
-        <v>0.137118228975148</v>
-      </c>
-      <c r="D4" s="19">
-        <v>2.7434677214941298E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>3.6492936678221601E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>7.6045396613461103E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>5.6330749815250401E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>7.1996794105151904E-2</v>
-      </c>
-      <c r="I4" s="19">
-        <v>0.135171665316001</v>
-      </c>
-      <c r="J4" s="19">
-        <v>3.9599048941661899E-2</v>
+      <c r="B4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.138236545971818</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2.724710281517E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>3.6983976454850603E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>7.5167327513895196E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>5.5988179066308298E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>7.0679895700990494E-2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.13605701243004301</v>
+      </c>
+      <c r="J4" s="9">
+        <v>4.0251409967432303E-2</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="7">
         <v>3</v>
       </c>
-      <c r="D5" s="17">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17">
-        <v>0</v>
-      </c>
-      <c r="F5" s="17">
-        <v>1</v>
-      </c>
-      <c r="G5" s="17">
-        <v>1</v>
-      </c>
-      <c r="H5" s="17">
-        <v>1</v>
-      </c>
-      <c r="I5" s="17">
-        <v>2</v>
-      </c>
-      <c r="J5" s="17">
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>2</v>
+      </c>
+      <c r="J5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5597,19 +5763,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -5618,7 +5784,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
@@ -5626,7 +5792,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -5644,7 +5810,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
@@ -5655,7 +5821,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -5673,88 +5839,86 @@
         <v>1</v>
       </c>
       <c r="I8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H10" s="5"/>
-    </row>
+    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="10"/>
-      <c r="L15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
+      <c r="L15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="10"/>
+    <row r="16" spans="2:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
       <c r="L16" s="1" t="s">
         <v>2</v>
       </c>
@@ -5763,32 +5927,32 @@
       </c>
     </row>
     <row r="17" spans="2:13" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
       <c r="L17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
       <c r="L18" s="1" t="s">
         <v>4</v>
       </c>
@@ -5797,15 +5961,15 @@
       </c>
     </row>
     <row r="19" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="18"/>
       <c r="L19" s="1" t="s">
         <v>5</v>
       </c>
@@ -5834,31 +5998,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5866,87 +6030,87 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
-        <v>2</v>
-      </c>
-      <c r="D3" s="16">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
-        <v>0</v>
-      </c>
-      <c r="G3" s="16">
-        <v>1</v>
-      </c>
-      <c r="H3" s="16">
-        <v>0</v>
-      </c>
-      <c r="I3" s="16">
-        <v>2</v>
-      </c>
-      <c r="J3" s="16">
+      <c r="C3" s="6">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>2</v>
+      </c>
+      <c r="J3" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>7.3054214161490896E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>2.9370973770186E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>4.2411369484607997E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>5.2146707174568499E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>9.0177984892149898E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>6.2929983612841203E-2</v>
-      </c>
-      <c r="I4" s="19">
-        <v>9.9119332995619897E-2</v>
-      </c>
-      <c r="J4" s="19">
-        <v>0.10023022775999001</v>
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>7.2914377198719696E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2.96789460549748E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>4.2540185893059197E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>5.1606013871418402E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>8.9643583160075702E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>6.3342529741268305E-2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>9.8336540692444005E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>9.8037819109198399E-2</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
-        <v>1</v>
-      </c>
-      <c r="D5" s="17">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17">
-        <v>0</v>
-      </c>
-      <c r="F5" s="17">
-        <v>1</v>
-      </c>
-      <c r="G5" s="17">
-        <v>1</v>
-      </c>
-      <c r="H5" s="17">
-        <v>1</v>
-      </c>
-      <c r="I5" s="17">
-        <v>1</v>
-      </c>
-      <c r="J5" s="17">
-        <v>2</v>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>2</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
@@ -5960,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -5972,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -6036,82 +6200,80 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="5"/>
-    </row>
+    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="10"/>
-      <c r="L15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
+      <c r="L15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="10"/>
+    <row r="16" spans="2:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
       <c r="L16" s="1" t="s">
         <v>2</v>
       </c>
@@ -6120,32 +6282,32 @@
       </c>
     </row>
     <row r="17" spans="2:13" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
       <c r="L17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
       <c r="L18" s="1" t="s">
         <v>4</v>
       </c>
@@ -6154,15 +6316,15 @@
       </c>
     </row>
     <row r="19" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="18"/>
       <c r="L19" s="1" t="s">
         <v>5</v>
       </c>
@@ -6191,31 +6353,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -6223,84 +6385,86 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="6">
         <v>3</v>
       </c>
-      <c r="D3" s="16">
-        <v>2</v>
-      </c>
-      <c r="E3" s="16">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16">
-        <v>0</v>
-      </c>
-      <c r="G3" s="16">
-        <v>0</v>
-      </c>
-      <c r="H3" s="16">
-        <v>1</v>
-      </c>
-      <c r="I3" s="16">
-        <v>1</v>
-      </c>
-      <c r="J3" s="16">
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>1</v>
+      </c>
+      <c r="J3" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>0.212910685122874</v>
-      </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19">
-        <v>2.1629165227494401E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>4.5426042532319903E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>9.1946159479101605E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>7.3181376979759696E-2</v>
-      </c>
-      <c r="I4" s="19">
-        <v>9.1697276266638497E-2</v>
-      </c>
-      <c r="J4" s="19">
-        <v>0.105003422650031</v>
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.211765530670918</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2.8052884068157698E-3</v>
+      </c>
+      <c r="E4" s="9">
+        <v>2.1466248200233701E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>4.4641053023677803E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>9.0729372971202302E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>7.3315633323320903E-2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>9.36261228456442E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0.103794865224275</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="7">
         <v>4</v>
       </c>
-      <c r="D5" s="17">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17">
-        <v>0</v>
-      </c>
-      <c r="F5" s="17">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17">
-        <v>1</v>
-      </c>
-      <c r="H5" s="17">
-        <v>1</v>
-      </c>
-      <c r="I5" s="17">
-        <v>1</v>
-      </c>
-      <c r="J5" s="17">
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
         <v>1</v>
       </c>
     </row>
@@ -6309,7 +6473,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -6318,7 +6482,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -6367,7 +6531,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -6376,7 +6540,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -6391,82 +6555,80 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="5"/>
-    </row>
+    <row r="10" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="10"/>
-      <c r="L15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
+      <c r="L15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="10"/>
+    <row r="16" spans="2:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
       <c r="L16" s="1" t="s">
         <v>2</v>
       </c>
@@ -6475,32 +6637,32 @@
       </c>
     </row>
     <row r="17" spans="2:13" ht="74" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
       <c r="L17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
       <c r="L18" s="1" t="s">
         <v>4</v>
       </c>
@@ -6509,15 +6671,15 @@
       </c>
     </row>
     <row r="19" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="18"/>
       <c r="L19" s="1" t="s">
         <v>5</v>
       </c>
@@ -6541,29 +6703,29 @@
   <cols>
     <col min="8" max="8" width="13.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.26953125" customWidth="1"/>
-    <col min="11" max="11" width="36.54296875" customWidth="1"/>
+    <col min="11" max="11" width="44.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -6571,68 +6733,68 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16">
-        <v>1</v>
-      </c>
-      <c r="H3" s="16">
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>9.2454816208020194E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>8.1785327677140807E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>9.3207521065826998E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>4.5849186065425103E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>0.10328097803021601</v>
-      </c>
-      <c r="H4" s="19">
-        <v>9.9945968280202094E-2</v>
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>9.2033063756391906E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>8.1980816083596197E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>9.2174263666557593E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>4.4946785052229099E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>9.9153097021756606E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.100754474480617</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
-        <v>1</v>
-      </c>
-      <c r="D5" s="17">
-        <v>1</v>
-      </c>
-      <c r="E5" s="17">
-        <v>1</v>
-      </c>
-      <c r="F5" s="17">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17">
-        <v>1</v>
-      </c>
-      <c r="H5" s="17">
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
         <v>1</v>
       </c>
     </row>
@@ -6705,70 +6867,68 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G10" s="5"/>
-    </row>
+    <row r="10" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="10"/>
-      <c r="J15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15"/>
+      <c r="J15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="10"/>
+    <row r="16" spans="2:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="15"/>
       <c r="J16" s="1" t="s">
         <v>2</v>
       </c>
@@ -6776,29 +6936,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="10"/>
+    <row r="17" spans="2:11" ht="71" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="15"/>
       <c r="J17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15"/>
       <c r="J18" s="1" t="s">
         <v>4</v>
       </c>
@@ -6806,14 +6966,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="13"/>
+    <row r="19" spans="2:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
       <c r="J19" s="1" t="s">
         <v>5</v>
       </c>
@@ -6841,28 +7001,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6870,77 +7030,77 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16">
-        <v>0</v>
-      </c>
-      <c r="D3" s="16">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16">
-        <v>1</v>
-      </c>
-      <c r="H3" s="16">
-        <v>0</v>
-      </c>
-      <c r="I3" s="16">
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="19">
-        <v>5.5276056905080799E-2</v>
-      </c>
-      <c r="D4" s="19">
-        <v>2.91065753550908E-2</v>
-      </c>
-      <c r="E4" s="19">
-        <v>5.8722877559649299E-2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>9.6126965237518097E-2</v>
-      </c>
-      <c r="G4" s="19">
-        <v>8.1181984207764804E-2</v>
-      </c>
-      <c r="H4" s="19">
-        <v>0.12865004442425099</v>
-      </c>
-      <c r="I4" s="19">
-        <v>0.107837747597492</v>
+      <c r="B4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="9">
+        <v>5.5132353860329303E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2.9524114835044E-2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>5.8547807274875401E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>9.6665799697972205E-2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>8.0568005629247805E-2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.127332297003312</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.108366651141878</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17">
-        <v>0</v>
-      </c>
-      <c r="F5" s="17">
-        <v>1</v>
-      </c>
-      <c r="G5" s="17">
-        <v>1</v>
-      </c>
-      <c r="H5" s="17">
-        <v>2</v>
-      </c>
-      <c r="I5" s="17">
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>2</v>
+      </c>
+      <c r="I5" s="7">
         <v>1</v>
       </c>
     </row>
@@ -6949,22 +7109,22 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -7001,7 +7161,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -7013,7 +7173,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -7024,72 +7184,72 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
+      <c r="B11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="10"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="10"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="10"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="10"/>
-      <c r="K15" s="4" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
+      <c r="K15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="10"/>
+    <row r="16" spans="2:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
       <c r="K16" s="1" t="s">
         <v>2</v>
       </c>
@@ -7098,30 +7258,30 @@
       </c>
     </row>
     <row r="17" spans="2:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
       <c r="K17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="10"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
       <c r="K18" s="1" t="s">
         <v>4</v>
       </c>
@@ -7130,14 +7290,14 @@
       </c>
     </row>
     <row r="19" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="18"/>
       <c r="K19" s="1" t="s">
         <v>5</v>
       </c>
